--- a/2026_B题/outputs/task_schedule_detail.xlsx
+++ b/2026_B题/outputs/task_schedule_detail.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -478,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,16 +481,16 @@
         <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>18.4410683947705</v>
+        <v>16.50916702272687</v>
       </c>
       <c r="F2" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H2" t="n">
-        <v>78.31635261010109</v>
+        <v>332.4298100159648</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -511,7 +499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,16 +514,16 @@
         <v>477.5</v>
       </c>
       <c r="E3" t="n">
-        <v>17.41269580752055</v>
+        <v>24.94856294391301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H3" t="n">
-        <v>331.3907796590553</v>
+        <v>121.9798731864522</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -544,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,16 +547,16 @@
         <v>481.5</v>
       </c>
       <c r="E4" t="n">
-        <v>22.26297182994274</v>
+        <v>20.9297249780839</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H4" t="n">
-        <v>308.9961237089955</v>
+        <v>133.4379746373003</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -577,7 +565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,22 +574,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481.5</v>
+        <v>481.7</v>
       </c>
       <c r="D5" t="n">
-        <v>482</v>
+        <v>482.2</v>
       </c>
       <c r="E5" t="n">
-        <v>20.75981765389583</v>
+        <v>22.5202231713943</v>
       </c>
       <c r="F5" t="n">
-        <v>1.03671884114252</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H5" t="n">
-        <v>133.4183896924487</v>
+        <v>309.4005358536368</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -625,16 +613,16 @@
         <v>488.9</v>
       </c>
       <c r="E6" t="n">
-        <v>14.78983151306694</v>
+        <v>14.78983151306692</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G6" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H6" t="n">
-        <v>70.92942721815609</v>
+        <v>70.92942721815615</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -643,7 +631,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -658,16 +646,16 @@
         <v>493.1</v>
       </c>
       <c r="E7" t="n">
-        <v>33.65711733847974</v>
+        <v>28.92786315958246</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3855700571420326</v>
+        <v>0.3855700571420329</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4931096392336043</v>
+        <v>0.4931096392337408</v>
       </c>
       <c r="H7" t="n">
-        <v>13.40562395961297</v>
+        <v>292.6498326275606</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -676,7 +664,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -691,16 +679,16 @@
         <v>493.6</v>
       </c>
       <c r="E8" t="n">
-        <v>19.15443455205088</v>
+        <v>28.50301986722616</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3075480024199045</v>
+        <v>0.3075480024199032</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6050145883315989</v>
+        <v>0.6050145883316765</v>
       </c>
       <c r="H8" t="n">
-        <v>35.3087823412576</v>
+        <v>323.5629353447528</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -709,7 +697,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -724,16 +712,16 @@
         <v>494.1</v>
       </c>
       <c r="E9" t="n">
-        <v>28.46025951461028</v>
+        <v>18.72619773433341</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6401969386332381</v>
+        <v>0.6401969386332378</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3327167018905053</v>
+        <v>0.33271670189047</v>
       </c>
       <c r="H9" t="n">
-        <v>322.6852204259091</v>
+        <v>35.02490904267194</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -742,7 +730,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -757,16 +745,16 @@
         <v>494.6</v>
       </c>
       <c r="E10" t="n">
-        <v>29.79128274077858</v>
+        <v>23.52207768816953</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7802312732734344</v>
+        <v>0.7802312732734343</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4997692472107983</v>
+        <v>0.4997692472106314</v>
       </c>
       <c r="H10" t="n">
-        <v>291.5171709854189</v>
+        <v>350.9126966384986</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -775,7 +763,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -790,16 +778,16 @@
         <v>495.1</v>
       </c>
       <c r="E11" t="n">
-        <v>23.04845870128828</v>
+        <v>32.6100984315562</v>
       </c>
       <c r="F11" t="n">
-        <v>1.475419714988617</v>
+        <v>1.475419714988615</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8210450087327569</v>
+        <v>0.821045008732599</v>
       </c>
       <c r="H11" t="n">
-        <v>349.7204874075622</v>
+        <v>11.2949302242838</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -823,13 +811,13 @@
         <v>508.7</v>
       </c>
       <c r="E12" t="n">
-        <v>16.09187826862355</v>
+        <v>16.09187826862361</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7632986234973324</v>
+        <v>0.7632986234973314</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2360869225073451</v>
+        <v>0.2360869225076145</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
@@ -839,7 +827,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -854,16 +842,16 @@
         <v>509.3</v>
       </c>
       <c r="E13" t="n">
-        <v>28.90017295275549</v>
+        <v>32.99986572350888</v>
       </c>
       <c r="F13" t="n">
-        <v>1.10284844547316</v>
+        <v>1.102848445473159</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1109048808462759</v>
+        <v>0.110904880846821</v>
       </c>
       <c r="H13" t="n">
-        <v>299.7176310038869</v>
+        <v>279.993298522834</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -872,7 +860,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -887,16 +875,16 @@
         <v>509.8</v>
       </c>
       <c r="E14" t="n">
-        <v>33.23924710940759</v>
+        <v>29.17336356608245</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5982877841336045</v>
+        <v>0.5982877841336044</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1344980702678082</v>
+        <v>0.1344980702672017</v>
       </c>
       <c r="H14" t="n">
-        <v>280.2389315442544</v>
+        <v>299.8226093374223</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -905,7 +893,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -914,19 +902,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>510.2</v>
+        <v>510.6</v>
       </c>
       <c r="D15" t="n">
-        <v>511.7</v>
+        <v>512.1</v>
       </c>
       <c r="E15" t="n">
-        <v>27.42574168610331</v>
+        <v>10.19933608780385</v>
       </c>
       <c r="F15" t="n">
-        <v>1.602191966144515</v>
+        <v>1.917472070147217</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5386540864605069</v>
+        <v>0.4765618512518291</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -936,7 +924,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -951,13 +939,13 @@
         <v>514.9</v>
       </c>
       <c r="E16" t="n">
-        <v>10.04439516364714</v>
+        <v>25.69177271173433</v>
       </c>
       <c r="F16" t="n">
         <v>1.605993802428558</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2681630642047913</v>
+        <v>0.2681630642051849</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -982,16 +970,16 @@
         <v>750.8</v>
       </c>
       <c r="E17" t="n">
-        <v>22.37801193007499</v>
+        <v>22.3780119300758</v>
       </c>
       <c r="F17" t="n">
-        <v>1.374773177086003</v>
+        <v>1.374773177086002</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1477724622783503</v>
+        <v>0.1477724622784411</v>
       </c>
       <c r="H17" t="n">
-        <v>269.2683666927907</v>
+        <v>269.2683666927891</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1000,7 +988,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1015,13 +1003,13 @@
         <v>752.5</v>
       </c>
       <c r="E18" t="n">
-        <v>11.06995835076455</v>
+        <v>16.65844527205057</v>
       </c>
       <c r="F18" t="n">
-        <v>1.905992447956873</v>
+        <v>1.905992447956871</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1945147114655638</v>
+        <v>0.1945147114663569</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1046,13 +1034,13 @@
         <v>763.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29.75104118834951</v>
+        <v>29.75104118834986</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9936591218759745</v>
+        <v>0.9936591218759739</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2743797737311392</v>
+        <v>0.2743797737319775</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">

--- a/2026_B题/outputs/task_schedule_detail.xlsx
+++ b/2026_B题/outputs/task_schedule_detail.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -466,7 +478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,16 +493,16 @@
         <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>16.50916702272687</v>
+        <v>18.32364434242325</v>
       </c>
       <c r="F2" t="n">
-        <v>1.089397535081515</v>
+        <v>1.0963632116626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3652891506872737</v>
+        <v>0.3635389276737643</v>
       </c>
       <c r="H2" t="n">
-        <v>332.4298100159648</v>
+        <v>78.50322981771842</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -499,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,16 +526,16 @@
         <v>477.5</v>
       </c>
       <c r="E3" t="n">
-        <v>24.94856294391301</v>
+        <v>17.39323042390096</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8653356928561704</v>
+        <v>0.8683134495735321</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4177629005766074</v>
+        <v>0.4187514451780422</v>
       </c>
       <c r="H3" t="n">
-        <v>121.9798731864522</v>
+        <v>330.9584587861622</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -532,7 +544,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -547,16 +559,16 @@
         <v>481.5</v>
       </c>
       <c r="E4" t="n">
-        <v>20.9297249780839</v>
+        <v>22.29724992008123</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8367785158010662</v>
+        <v>0.8363571031746303</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3160018881789212</v>
+        <v>0.3169657494272787</v>
       </c>
       <c r="H4" t="n">
-        <v>133.4379746373003</v>
+        <v>308.6716971776825</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -565,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -574,22 +586,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481.7</v>
+        <v>481.5</v>
       </c>
       <c r="D5" t="n">
-        <v>482.2</v>
+        <v>482</v>
       </c>
       <c r="E5" t="n">
-        <v>22.5202231713943</v>
+        <v>20.73783426178843</v>
       </c>
       <c r="F5" t="n">
-        <v>1.383708317324045</v>
+        <v>1.032208668939235</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5309158474563628</v>
+        <v>0.373067563677073</v>
       </c>
       <c r="H5" t="n">
-        <v>309.4005358536368</v>
+        <v>133.7653436477757</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -613,16 +625,16 @@
         <v>488.9</v>
       </c>
       <c r="E6" t="n">
-        <v>14.78983151306692</v>
+        <v>14.66954673566903</v>
       </c>
       <c r="F6" t="n">
-        <v>1.290366607856749</v>
+        <v>1.287848736592751</v>
       </c>
       <c r="G6" t="n">
-        <v>1.268558534998151</v>
+        <v>1.267301538357044</v>
       </c>
       <c r="H6" t="n">
-        <v>70.92942721815615</v>
+        <v>71.1096553597875</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -631,7 +643,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -646,16 +658,16 @@
         <v>493.1</v>
       </c>
       <c r="E7" t="n">
-        <v>28.92786315958246</v>
+        <v>33.56165314050959</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3855700571420329</v>
+        <v>0.3841216179500924</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4931096392337408</v>
+        <v>0.4936339235364541</v>
       </c>
       <c r="H7" t="n">
-        <v>292.6498326275606</v>
+        <v>13.26722165403316</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -664,7 +676,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -679,16 +691,16 @@
         <v>493.6</v>
       </c>
       <c r="E8" t="n">
-        <v>28.50301986722616</v>
+        <v>19.03579422610053</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3075480024199032</v>
+        <v>0.3067760547763279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6050145883316765</v>
+        <v>0.6054512777350793</v>
       </c>
       <c r="H8" t="n">
-        <v>323.5629353447528</v>
+        <v>35.1911451533897</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -697,7 +709,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,16 +724,16 @@
         <v>494.1</v>
       </c>
       <c r="E9" t="n">
-        <v>18.72619773433341</v>
+        <v>28.46084326420071</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6401969386332378</v>
+        <v>0.640356420688205</v>
       </c>
       <c r="G9" t="n">
-        <v>0.33271670189047</v>
+        <v>0.3325233326922711</v>
       </c>
       <c r="H9" t="n">
-        <v>35.02490904267194</v>
+        <v>322.4342997022272</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -730,7 +742,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -745,16 +757,16 @@
         <v>494.6</v>
       </c>
       <c r="E10" t="n">
-        <v>23.52207768816953</v>
+        <v>29.86149126251642</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7802312732734343</v>
+        <v>0.7778113873489794</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4997692472106314</v>
+        <v>0.4976135725272782</v>
       </c>
       <c r="H10" t="n">
-        <v>350.9126966384986</v>
+        <v>291.3169522682211</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -763,7 +775,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -778,16 +790,16 @@
         <v>495.1</v>
       </c>
       <c r="E11" t="n">
-        <v>32.6100984315562</v>
+        <v>22.99208621713783</v>
       </c>
       <c r="F11" t="n">
-        <v>1.475419714988615</v>
+        <v>1.474287787516881</v>
       </c>
       <c r="G11" t="n">
-        <v>0.821045008732599</v>
+        <v>0.8241322598369778</v>
       </c>
       <c r="H11" t="n">
-        <v>11.2949302242838</v>
+        <v>349.4506019315439</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -796,7 +808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -811,13 +823,13 @@
         <v>508.7</v>
       </c>
       <c r="E12" t="n">
-        <v>16.09187826862361</v>
+        <v>26.66308133646042</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7632986234973314</v>
+        <v>0.7624385138333061</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2360869225076145</v>
+        <v>0.2357637531709909</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
@@ -827,7 +839,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -842,16 +854,16 @@
         <v>509.3</v>
       </c>
       <c r="E13" t="n">
-        <v>32.99986572350888</v>
+        <v>28.95494731989802</v>
       </c>
       <c r="F13" t="n">
-        <v>1.102848445473159</v>
+        <v>1.106931806431469</v>
       </c>
       <c r="G13" t="n">
-        <v>0.110904880846821</v>
+        <v>0.1134330201213349</v>
       </c>
       <c r="H13" t="n">
-        <v>279.993298522834</v>
+        <v>299.4932790019222</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -860,7 +872,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -869,22 +881,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>509.3</v>
+        <v>509.8</v>
       </c>
       <c r="D14" t="n">
-        <v>509.8</v>
+        <v>510.3</v>
       </c>
       <c r="E14" t="n">
-        <v>29.17336356608245</v>
+        <v>33.7429751357474</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5982877841336044</v>
+        <v>0.5898368486750509</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1344980702672017</v>
+        <v>0.2480700076951234</v>
       </c>
       <c r="H14" t="n">
-        <v>299.8226093374223</v>
+        <v>280.1953273208402</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -893,7 +905,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -908,13 +920,13 @@
         <v>512.1</v>
       </c>
       <c r="E15" t="n">
-        <v>10.19933608780385</v>
+        <v>18.11913278404953</v>
       </c>
       <c r="F15" t="n">
-        <v>1.917472070147217</v>
+        <v>1.918208752693482</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4765618512518291</v>
+        <v>0.4759644820656086</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -924,7 +936,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -939,13 +951,13 @@
         <v>514.9</v>
       </c>
       <c r="E16" t="n">
-        <v>25.69177271173433</v>
+        <v>10.00341585638209</v>
       </c>
       <c r="F16" t="n">
-        <v>1.605993802428558</v>
+        <v>1.604412901025261</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2681630642051849</v>
+        <v>0.2683907458179484</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -970,16 +982,16 @@
         <v>750.8</v>
       </c>
       <c r="E17" t="n">
-        <v>22.3780119300758</v>
+        <v>22.48319288510971</v>
       </c>
       <c r="F17" t="n">
-        <v>1.374773177086002</v>
+        <v>1.372928021955616</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1477724622784411</v>
+        <v>0.1505902973488793</v>
       </c>
       <c r="H17" t="n">
-        <v>269.2683666927891</v>
+        <v>269.0805451334944</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -988,7 +1000,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1003,13 +1015,13 @@
         <v>752.5</v>
       </c>
       <c r="E18" t="n">
-        <v>16.65844527205057</v>
+        <v>10.94305178781901</v>
       </c>
       <c r="F18" t="n">
-        <v>1.905992447956871</v>
+        <v>1.905336777270484</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1945147114663569</v>
+        <v>0.1917051844304302</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1034,13 +1046,13 @@
         <v>763.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29.75104118834986</v>
+        <v>29.73310582565653</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9936591218759739</v>
+        <v>0.9916570095933905</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2743797737319775</v>
+        <v>0.2767023682100468</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">

--- a/2026_B题/outputs/task_schedule_detail.xlsx
+++ b/2026_B题/outputs/task_schedule_detail.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -499,10 +487,10 @@
         <v>1.0963632116626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H2" t="n">
-        <v>78.50322981771842</v>
+        <v>78.50322981771848</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -526,13 +514,13 @@
         <v>477.5</v>
       </c>
       <c r="E3" t="n">
-        <v>17.39323042390096</v>
+        <v>17.39323042390095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H3" t="n">
         <v>330.9584587861622</v>
@@ -559,13 +547,13 @@
         <v>481.5</v>
       </c>
       <c r="E4" t="n">
-        <v>22.29724992008123</v>
+        <v>22.29724992008122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H4" t="n">
         <v>308.6716971776825</v>
@@ -586,22 +574,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481.5</v>
+        <v>481.7</v>
       </c>
       <c r="D5" t="n">
-        <v>482</v>
+        <v>482.2</v>
       </c>
       <c r="E5" t="n">
-        <v>20.73783426178843</v>
+        <v>20.63985779840226</v>
       </c>
       <c r="F5" t="n">
-        <v>1.032208668939235</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.373067563677073</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H5" t="n">
-        <v>133.7653436477757</v>
+        <v>133.4132475672204</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -625,13 +613,13 @@
         <v>488.9</v>
       </c>
       <c r="E6" t="n">
-        <v>14.66954673566903</v>
+        <v>14.66954673566902</v>
       </c>
       <c r="F6" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G6" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H6" t="n">
         <v>71.1096553597875</v>
@@ -661,10 +649,10 @@
         <v>33.56165314050959</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3841216179500924</v>
+        <v>0.3841216179500925</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4936339235364541</v>
+        <v>0.4936339235364577</v>
       </c>
       <c r="H7" t="n">
         <v>13.26722165403316</v>
@@ -694,10 +682,10 @@
         <v>19.03579422610053</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3067760547763279</v>
+        <v>0.3067760547763284</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6054512777350793</v>
+        <v>0.6054512777350818</v>
       </c>
       <c r="H8" t="n">
         <v>35.1911451533897</v>
@@ -724,16 +712,16 @@
         <v>494.1</v>
       </c>
       <c r="E9" t="n">
-        <v>28.46084326420071</v>
+        <v>28.46084326420072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.640356420688205</v>
+        <v>0.6403564206882054</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3325233326922711</v>
+        <v>0.3325233326922695</v>
       </c>
       <c r="H9" t="n">
-        <v>322.4342997022272</v>
+        <v>322.4342997022271</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -757,13 +745,13 @@
         <v>494.6</v>
       </c>
       <c r="E10" t="n">
-        <v>29.86149126251642</v>
+        <v>29.86149126251643</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7778113873489794</v>
+        <v>0.7778113873489795</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4976135725272782</v>
+        <v>0.497613572527272</v>
       </c>
       <c r="H10" t="n">
         <v>291.3169522682211</v>
@@ -793,10 +781,10 @@
         <v>22.99208621713783</v>
       </c>
       <c r="F11" t="n">
-        <v>1.474287787516881</v>
+        <v>1.474287787516882</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8241322598369778</v>
+        <v>0.8241322598369721</v>
       </c>
       <c r="H11" t="n">
         <v>349.4506019315439</v>
@@ -823,13 +811,13 @@
         <v>508.7</v>
       </c>
       <c r="E12" t="n">
-        <v>26.66308133646042</v>
+        <v>26.66308133646041</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7624385138333061</v>
+        <v>0.7624385138333066</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2357637531709909</v>
+        <v>0.2357637531709994</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
@@ -854,16 +842,16 @@
         <v>509.3</v>
       </c>
       <c r="E13" t="n">
-        <v>28.95494731989802</v>
+        <v>28.95494731989805</v>
       </c>
       <c r="F13" t="n">
         <v>1.106931806431469</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1134330201213349</v>
+        <v>0.1134330201213506</v>
       </c>
       <c r="H13" t="n">
-        <v>299.4932790019222</v>
+        <v>299.4932790019221</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -881,22 +869,22 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>509.3</v>
+      </c>
+      <c r="D14" t="n">
         <v>509.8</v>
       </c>
-      <c r="D14" t="n">
-        <v>510.3</v>
-      </c>
       <c r="E14" t="n">
-        <v>33.7429751357474</v>
+        <v>33.32727092554418</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5898368486750509</v>
+        <v>0.598639043114917</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2480700076951234</v>
+        <v>0.1336178658726302</v>
       </c>
       <c r="H14" t="n">
-        <v>280.1953273208402</v>
+        <v>280.0815821922205</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -905,7 +893,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -914,19 +902,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>510.6</v>
+        <v>510.2</v>
       </c>
       <c r="D15" t="n">
-        <v>512.1</v>
+        <v>511.7</v>
       </c>
       <c r="E15" t="n">
-        <v>18.11913278404953</v>
+        <v>10.42632760718104</v>
       </c>
       <c r="F15" t="n">
-        <v>1.918208752693482</v>
+        <v>1.60110858502629</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4759644820656086</v>
+        <v>0.539443631924745</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -936,7 +924,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -951,13 +939,13 @@
         <v>514.9</v>
       </c>
       <c r="E16" t="n">
-        <v>10.00341585638209</v>
+        <v>19.61096710531255</v>
       </c>
       <c r="F16" t="n">
         <v>1.604412901025261</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2683907458179484</v>
+        <v>0.2683907458179609</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -982,13 +970,13 @@
         <v>750.8</v>
       </c>
       <c r="E17" t="n">
-        <v>22.48319288510971</v>
+        <v>22.48319288510975</v>
       </c>
       <c r="F17" t="n">
         <v>1.372928021955616</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1505902973488793</v>
+        <v>0.1505902973488805</v>
       </c>
       <c r="H17" t="n">
         <v>269.0805451334944</v>
@@ -1000,7 +988,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1015,13 +1003,13 @@
         <v>752.5</v>
       </c>
       <c r="E18" t="n">
-        <v>10.94305178781901</v>
+        <v>16.58899498636473</v>
       </c>
       <c r="F18" t="n">
-        <v>1.905336777270484</v>
+        <v>1.905336777270485</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1917051844304302</v>
+        <v>0.1917051844304548</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1046,13 +1034,13 @@
         <v>763.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29.73310582565653</v>
+        <v>29.73310582565654</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9916570095933905</v>
+        <v>0.9916570095933909</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2767023682100468</v>
+        <v>0.276702368210072</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">

--- a/2026_B题/outputs/task_schedule_detail.xlsx
+++ b/2026_B题/outputs/task_schedule_detail.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -493,16 +481,16 @@
         <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>18.4410683947705</v>
+        <v>18.32364434242325</v>
       </c>
       <c r="F2" t="n">
-        <v>1.089397535081516</v>
+        <v>1.0963632116626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H2" t="n">
-        <v>78.31635261010109</v>
+        <v>78.50322981771848</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -526,16 +514,16 @@
         <v>477.5</v>
       </c>
       <c r="E3" t="n">
-        <v>17.41269580752055</v>
+        <v>17.39323042390095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H3" t="n">
-        <v>331.3907796590553</v>
+        <v>330.9584587861622</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -559,16 +547,16 @@
         <v>481.5</v>
       </c>
       <c r="E4" t="n">
-        <v>22.26297182994274</v>
+        <v>22.29724992008122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H4" t="n">
-        <v>308.9961237089955</v>
+        <v>308.6716971776825</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -586,22 +574,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481.5</v>
+        <v>481.7</v>
       </c>
       <c r="D5" t="n">
-        <v>482</v>
+        <v>482.2</v>
       </c>
       <c r="E5" t="n">
-        <v>20.75981765389583</v>
+        <v>20.63985779840226</v>
       </c>
       <c r="F5" t="n">
-        <v>1.03671884114252</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H5" t="n">
-        <v>133.4183896924487</v>
+        <v>133.4132475672204</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -625,16 +613,16 @@
         <v>488.9</v>
       </c>
       <c r="E6" t="n">
-        <v>14.78983151306694</v>
+        <v>14.66954673566902</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29036660785675</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G6" t="n">
-        <v>1.268558534998172</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H6" t="n">
-        <v>70.92942721815609</v>
+        <v>71.1096553597875</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -658,16 +646,16 @@
         <v>493.1</v>
       </c>
       <c r="E7" t="n">
-        <v>33.65711733847974</v>
+        <v>33.56165314050959</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3855700571420326</v>
+        <v>0.3841216179500925</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4931096392336043</v>
+        <v>0.4936339235364577</v>
       </c>
       <c r="H7" t="n">
-        <v>13.40562395961297</v>
+        <v>13.26722165403316</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -691,16 +679,16 @@
         <v>493.6</v>
       </c>
       <c r="E8" t="n">
-        <v>19.15443455205088</v>
+        <v>19.03579422610053</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3075480024199045</v>
+        <v>0.3067760547763284</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6050145883315989</v>
+        <v>0.6054512777350818</v>
       </c>
       <c r="H8" t="n">
-        <v>35.3087823412576</v>
+        <v>35.1911451533897</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -724,16 +712,16 @@
         <v>494.1</v>
       </c>
       <c r="E9" t="n">
-        <v>28.46025951461028</v>
+        <v>28.46084326420072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6401969386332381</v>
+        <v>0.6403564206882054</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3327167018905053</v>
+        <v>0.3325233326922695</v>
       </c>
       <c r="H9" t="n">
-        <v>322.6852204259091</v>
+        <v>322.4342997022271</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -757,16 +745,16 @@
         <v>494.6</v>
       </c>
       <c r="E10" t="n">
-        <v>29.79128274077858</v>
+        <v>29.86149126251643</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7802312732734344</v>
+        <v>0.7778113873489795</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4997692472107983</v>
+        <v>0.497613572527272</v>
       </c>
       <c r="H10" t="n">
-        <v>291.5171709854189</v>
+        <v>291.3169522682211</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -790,16 +778,16 @@
         <v>495.1</v>
       </c>
       <c r="E11" t="n">
-        <v>23.04845870128828</v>
+        <v>22.99208621713783</v>
       </c>
       <c r="F11" t="n">
-        <v>1.475419714988617</v>
+        <v>1.474287787516882</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8210450087327569</v>
+        <v>0.8241322598369721</v>
       </c>
       <c r="H11" t="n">
-        <v>349.7204874075622</v>
+        <v>349.4506019315439</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -808,7 +796,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -823,13 +811,13 @@
         <v>508.7</v>
       </c>
       <c r="E12" t="n">
-        <v>16.09187826862355</v>
+        <v>26.66308133646041</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7632986234973324</v>
+        <v>0.7624385138333066</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2360869225073451</v>
+        <v>0.2357637531709994</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
@@ -854,16 +842,16 @@
         <v>509.3</v>
       </c>
       <c r="E13" t="n">
-        <v>28.90017295275549</v>
+        <v>28.95494731989805</v>
       </c>
       <c r="F13" t="n">
-        <v>1.10284844547316</v>
+        <v>1.106931806431469</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1109048808462759</v>
+        <v>0.1134330201213506</v>
       </c>
       <c r="H13" t="n">
-        <v>299.7176310038869</v>
+        <v>299.4932790019221</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -887,16 +875,16 @@
         <v>509.8</v>
       </c>
       <c r="E14" t="n">
-        <v>33.23924710940759</v>
+        <v>33.32727092554418</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5982877841336045</v>
+        <v>0.598639043114917</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1344980702678082</v>
+        <v>0.1336178658726302</v>
       </c>
       <c r="H14" t="n">
-        <v>280.2389315442544</v>
+        <v>280.0815821922205</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -905,7 +893,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -920,13 +908,13 @@
         <v>511.7</v>
       </c>
       <c r="E15" t="n">
-        <v>27.42574168610331</v>
+        <v>10.42632760718104</v>
       </c>
       <c r="F15" t="n">
-        <v>1.602191966144515</v>
+        <v>1.60110858502629</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5386540864605069</v>
+        <v>0.539443631924745</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -936,7 +924,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -951,13 +939,13 @@
         <v>514.9</v>
       </c>
       <c r="E16" t="n">
-        <v>10.04439516364714</v>
+        <v>19.61096710531255</v>
       </c>
       <c r="F16" t="n">
-        <v>1.605993802428558</v>
+        <v>1.604412901025261</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2681630642047913</v>
+        <v>0.2683907458179609</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -982,16 +970,16 @@
         <v>750.8</v>
       </c>
       <c r="E17" t="n">
-        <v>22.37801193007499</v>
+        <v>22.48319288510975</v>
       </c>
       <c r="F17" t="n">
-        <v>1.374773177086003</v>
+        <v>1.372928021955616</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1477724622783503</v>
+        <v>0.1505902973488805</v>
       </c>
       <c r="H17" t="n">
-        <v>269.2683666927907</v>
+        <v>269.0805451334944</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1000,7 +988,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1015,13 +1003,13 @@
         <v>752.5</v>
       </c>
       <c r="E18" t="n">
-        <v>11.06995835076455</v>
+        <v>16.58899498636473</v>
       </c>
       <c r="F18" t="n">
-        <v>1.905992447956873</v>
+        <v>1.905336777270485</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1945147114655638</v>
+        <v>0.1917051844304548</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1046,13 +1034,13 @@
         <v>763.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29.75104118834951</v>
+        <v>29.73310582565654</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9936591218759745</v>
+        <v>0.9916570095933909</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2743797737311392</v>
+        <v>0.276702368210072</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">

--- a/2026_B题/outputs/task_schedule_detail.xlsx
+++ b/2026_B题/outputs/task_schedule_detail.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -466,7 +478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,16 +493,16 @@
         <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>18.32364434242325</v>
+        <v>20.27576330244549</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H2" t="n">
-        <v>78.50322981771848</v>
+        <v>19.16402307633621</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -499,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,16 +526,16 @@
         <v>477.5</v>
       </c>
       <c r="E3" t="n">
-        <v>17.39323042390095</v>
+        <v>19.93508148045045</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H3" t="n">
-        <v>330.9584587861622</v>
+        <v>289.0489974636989</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -532,7 +544,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -547,16 +559,16 @@
         <v>481.5</v>
       </c>
       <c r="E4" t="n">
-        <v>22.29724992008122</v>
+        <v>20.90607911535624</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H4" t="n">
-        <v>308.6716971776825</v>
+        <v>133.7901506552606</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -565,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -574,22 +586,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481.7</v>
+        <v>481.5</v>
       </c>
       <c r="D5" t="n">
-        <v>482.2</v>
+        <v>482</v>
       </c>
       <c r="E5" t="n">
-        <v>20.63985779840226</v>
+        <v>23.84446236586811</v>
       </c>
       <c r="F5" t="n">
-        <v>1.375716985626096</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G5" t="n">
-        <v>0.530587150405935</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H5" t="n">
-        <v>133.4132475672204</v>
+        <v>342.6173494649422</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -613,13 +625,13 @@
         <v>488.9</v>
       </c>
       <c r="E6" t="n">
-        <v>14.66954673566902</v>
+        <v>14.66954673566905</v>
       </c>
       <c r="F6" t="n">
         <v>1.287848736592752</v>
       </c>
       <c r="G6" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H6" t="n">
         <v>71.1096553597875</v>
@@ -631,7 +643,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -646,16 +658,16 @@
         <v>493.1</v>
       </c>
       <c r="E7" t="n">
-        <v>33.56165314050959</v>
+        <v>18.95471440698913</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3841216179500925</v>
+        <v>0.3841216179500923</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4936339235364577</v>
+        <v>0.4936339235363214</v>
       </c>
       <c r="H7" t="n">
-        <v>13.26722165403316</v>
+        <v>37.36016174669413</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -664,7 +676,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -679,16 +691,16 @@
         <v>493.6</v>
       </c>
       <c r="E8" t="n">
-        <v>19.03579422610053</v>
+        <v>29.67257920687645</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3067760547763284</v>
+        <v>0.3067760547763293</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6054512777350818</v>
+        <v>0.605451277735005</v>
       </c>
       <c r="H8" t="n">
-        <v>35.1911451533897</v>
+        <v>292.9217733735815</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -697,7 +709,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,16 +724,16 @@
         <v>494.1</v>
       </c>
       <c r="E9" t="n">
-        <v>28.46084326420072</v>
+        <v>23.84095350558757</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6403564206882054</v>
+        <v>0.6403564206882053</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3325233326922695</v>
+        <v>0.3325233326923064</v>
       </c>
       <c r="H9" t="n">
-        <v>322.4342997022271</v>
+        <v>351.1892615877132</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -730,7 +742,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -745,16 +757,16 @@
         <v>494.6</v>
       </c>
       <c r="E10" t="n">
-        <v>29.86149126251643</v>
+        <v>28.24466802072075</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7778113873489795</v>
+        <v>0.7778113873489796</v>
       </c>
       <c r="G10" t="n">
-        <v>0.497613572527272</v>
+        <v>0.4976135725274385</v>
       </c>
       <c r="H10" t="n">
-        <v>291.3169522682211</v>
+        <v>321.666321970858</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -763,7 +775,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -778,16 +790,16 @@
         <v>495.1</v>
       </c>
       <c r="E11" t="n">
-        <v>22.99208621713783</v>
+        <v>32.51771286355752</v>
       </c>
       <c r="F11" t="n">
-        <v>1.474287787516882</v>
+        <v>1.474287787516883</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8241322598369721</v>
+        <v>0.8241322598371309</v>
       </c>
       <c r="H11" t="n">
-        <v>349.4506019315439</v>
+        <v>11.15416272967195</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -796,7 +808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -811,13 +823,13 @@
         <v>508.7</v>
       </c>
       <c r="E12" t="n">
-        <v>26.66308133646041</v>
+        <v>16.02941273859052</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7624385138333066</v>
+        <v>0.7624385138333071</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2357637531709994</v>
+        <v>0.2357637531707255</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
@@ -842,16 +854,16 @@
         <v>509.3</v>
       </c>
       <c r="E13" t="n">
-        <v>28.95494731989805</v>
+        <v>28.95494731989739</v>
       </c>
       <c r="F13" t="n">
-        <v>1.106931806431469</v>
+        <v>1.10693180643147</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1134330201213506</v>
+        <v>0.1134330201208114</v>
       </c>
       <c r="H13" t="n">
-        <v>299.4932790019221</v>
+        <v>299.4932790019229</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -875,16 +887,16 @@
         <v>509.8</v>
       </c>
       <c r="E14" t="n">
-        <v>33.32727092554418</v>
+        <v>33.32727092554342</v>
       </c>
       <c r="F14" t="n">
-        <v>0.598639043114917</v>
+        <v>0.5986390431149172</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1336178658726302</v>
+        <v>0.133617865873239</v>
       </c>
       <c r="H14" t="n">
-        <v>280.0815821922205</v>
+        <v>280.0815821922208</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -908,13 +920,13 @@
         <v>511.7</v>
       </c>
       <c r="E15" t="n">
-        <v>10.42632760718104</v>
+        <v>10.42632760718119</v>
       </c>
       <c r="F15" t="n">
-        <v>1.60110858502629</v>
+        <v>1.601108585026291</v>
       </c>
       <c r="G15" t="n">
-        <v>0.539443631924745</v>
+        <v>0.5394436319252088</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -924,7 +936,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -939,13 +951,13 @@
         <v>514.9</v>
       </c>
       <c r="E16" t="n">
-        <v>19.61096710531255</v>
+        <v>25.60589084164459</v>
       </c>
       <c r="F16" t="n">
-        <v>1.604412901025261</v>
+        <v>1.604412901025263</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2683907458179609</v>
+        <v>0.2683907458175703</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -970,16 +982,16 @@
         <v>750.8</v>
       </c>
       <c r="E17" t="n">
-        <v>22.48319288510975</v>
+        <v>22.48319288510894</v>
       </c>
       <c r="F17" t="n">
-        <v>1.372928021955616</v>
+        <v>1.372928021955617</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1505902973488805</v>
+        <v>0.1505902973487885</v>
       </c>
       <c r="H17" t="n">
-        <v>269.0805451334944</v>
+        <v>269.0805451334959</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -988,7 +1000,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1003,13 +1015,13 @@
         <v>752.5</v>
       </c>
       <c r="E18" t="n">
-        <v>16.58899498636473</v>
+        <v>10.94305178781997</v>
       </c>
       <c r="F18" t="n">
-        <v>1.905336777270485</v>
+        <v>1.905336777270486</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1917051844304548</v>
+        <v>0.1917051844296607</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1034,13 +1046,13 @@
         <v>763.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29.73310582565654</v>
+        <v>29.73310582565619</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9916570095933909</v>
+        <v>0.9916570095933919</v>
       </c>
       <c r="G19" t="n">
-        <v>0.276702368210072</v>
+        <v>0.2767023682092388</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
